--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XL/LTAIPT_A63F40A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XL/LTAIPT_A63F40A.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
   <si>
     <t>49010</t>
   </si>
@@ -115,53 +115,34 @@
     <t>Nota</t>
   </si>
   <si>
+    <t>http://cobatlaxcala.edu.mx/COBAT/</t>
+  </si>
+  <si>
+    <t>Subdirección de Planeación y Evaluación</t>
+  </si>
+  <si>
+    <t>Sin nota</t>
+  </si>
+  <si>
+    <t>95546A4F7EA1F00D0DEE95FCFD4E0F44</t>
+  </si>
+  <si>
     <t>2022</t>
   </si>
   <si>
-    <t>Subdirección de Planeación y Evaluación</t>
-  </si>
-  <si>
-    <t>C36AEAED796DFAAEE04F83F5884A6E3F</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>Fondo de Aportaciones Múltiples (FAM) 2019</t>
-  </si>
-  <si>
-    <t>Evaluación de Consistencia y Resultados del Fondo de
-Aportaciones Múltiples (FAM), ejercicio fiscal 2019</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/portal/assets/archivos/pdf/evaluaciones_externas/NOTIFICACI%C3%93N_DE_CUMPLIMIENTO_EVALUACI%C3%93N_PAE.pdf</t>
-  </si>
-  <si>
-    <t>15/07/2022</t>
-  </si>
-  <si>
-    <t>En el periodo del 01 de abril de 2022 al 30 de junio de 2022, el Colegio de Bachilleres del Estado de Tlaxcala, no reportará ninguna evaluación a programas financiados con recursos públicos, sin embargo, si hubiera alguna evaluación a algún programa, se hará la actualización y validación dentro de los 15 días posteriores a la evaluación.</t>
-  </si>
-  <si>
-    <t>792B1C60AC35DCFD67E3CC0BA34D12D5</t>
-  </si>
-  <si>
-    <t>Fondo de Aportaciones Múltiples (FAM) 2018</t>
-  </si>
-  <si>
-    <t>Evaluación de Procesos    Ejercicio fiscal 2018</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/portal/evaluaciones_externas/index-FAM.html#</t>
-  </si>
-  <si>
-    <t>15DB79C7E7E9E2BA770EE141C7E12B04</t>
-  </si>
-  <si>
-    <t/>
+    <t>01/01/2022</t>
+  </si>
+  <si>
+    <t>31/12/2022</t>
+  </si>
+  <si>
+    <t>Fondo de Aportaciones Múltiples (FAM) 2022</t>
+  </si>
+  <si>
+    <t>Evaluación de Procesos    Ejercicio fiscal 2022</t>
+  </si>
+  <si>
+    <t>05/04/2023</t>
   </si>
 </sst>
 </file>
@@ -238,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -252,9 +233,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -557,20 +535,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.5703125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="126" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="39.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="255" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
@@ -723,107 +700,37 @@
     </row>
     <row r="8" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>34</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
